--- a/simulations/correction-peat-ind/impact_peat_corr.xlsx
+++ b/simulations/correction-peat-ind/impact_peat_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction-peat-ind\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36F11B3-4927-4020-89E5-2BEC6A0CB001}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B69666-2E89-498E-9B60-A28F42CD3140}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{9F4004D4-A1D9-4A72-950D-807AD9ECE5A0}"/>
   </bookViews>
@@ -578,39 +578,21 @@
       <sheetName val="AD_a_mid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="51">
-          <cell r="C51">
-            <v>-267.29345925553793</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="42">
-          <cell r="C42">
-            <v>-332.61769502520548</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="49">
-          <cell r="C49">
-            <v>-265.33407220943303</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
       <sheetData sheetId="15">
         <row r="87">
           <cell r="C87">
@@ -618,42 +600,18 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="16">
-        <row r="41">
-          <cell r="C41">
-            <v>-199.91210764074481</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="17">
-        <row r="50">
-          <cell r="C50">
-            <v>-114.56471032029754</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="18">
-        <row r="40">
-          <cell r="C40">
-            <v>-350.6814695298803</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
-        <row r="55">
-          <cell r="C55">
-            <v>-251.7873595492309</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -734,18 +692,18 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
       <sheetData sheetId="13">
         <row r="50">
           <cell r="C50">
@@ -762,9 +720,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="14">
-        <row r="30">
-          <cell r="AG30">
-            <v>45.531422488575686</v>
+        <row r="46">
+          <cell r="AG46">
+            <v>46.522352528175723</v>
           </cell>
         </row>
       </sheetData>
@@ -811,9 +769,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
       <sheetData sheetId="21">
         <row r="41">
           <cell r="C41">
@@ -844,13 +802,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1028,7 +986,7 @@
       <sheetName val="AD_a_mid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="28">
           <cell r="C28">
@@ -1066,43 +1024,19 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
-        <row r="24">
-          <cell r="E24">
-            <v>509.03089819946877</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
-        <row r="24">
-          <cell r="E24">
-            <v>509.03089819946877</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="11">
-        <row r="23">
-          <cell r="E23">
-            <v>131.83340888752835</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14">
-        <row r="15">
-          <cell r="E15">
-            <v>11.6046876865655</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
       <sheetData sheetId="15">
         <row r="75">
           <cell r="C75">
@@ -1110,16 +1044,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19">
-        <row r="25">
-          <cell r="E25">
-            <v>9.1614439984537466</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
       <sheetData sheetId="20">
         <row r="43">
           <cell r="C43">
@@ -1127,13 +1055,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
